--- a/app/templates/annex_template.xlsx
+++ b/app/templates/annex_template.xlsx
@@ -1,21 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="120" windowWidth="14940" windowHeight="9225" activeTab="0"/>
+    <workbookView windowWidth="28800" windowHeight="11730"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId5"/>
-  </externalReferences>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$AF$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$AF$25</definedName>
   </definedNames>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -148,26 +158,25 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;₱&quot;* #,##0_-;\-&quot;₱&quot;* #,##0_-;_-&quot;₱&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;₱&quot;* #,##0.00_-;\-&quot;₱&quot;* #,##0.00_-;_-&quot;₱&quot;* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -175,11 +184,169 @@
       <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -216,8 +383,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -236,6 +589,7 @@
         <color auto="1"/>
       </top>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -248,18 +602,37 @@
         <color auto="1"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color auto="1"/>
       </right>
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -268,12 +641,13 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color auto="1"/>
       </top>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -282,54 +656,56 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color auto="1"/>
       </top>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
       <right style="thin">
         <color auto="1"/>
       </right>
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color auto="1"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -338,40 +714,28 @@
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color auto="1"/>
       </top>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color auto="1"/>
       </right>
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -386,216 +750,617 @@
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="15" builtinId="5"/>
-    <cellStyle name="Currency" xfId="16" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
-    <cellStyle name="Comma" xfId="18" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>29</xdr:col>
@@ -611,21 +1376,17 @@
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Text Box 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{c85514d9-b5cb-486e-bad2-1d3360eadc2c}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2" name="Text Box 1"/>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18288000" y="47625"/>
-          <a:ext cx="1219200" cy="333375"/>
+          <a:off x="18002250" y="47625"/>
+          <a:ext cx="1200150" cy="337185"/>
         </a:xfrm>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
         <a:solidFill>
           <a:srgbClr val="FFFFFF"/>
         </a:solidFill>
@@ -636,8 +1397,7 @@
         </a:ln>
       </xdr:spPr>
       <xdr:txBody>
-        <a:bodyPr fromWordArt="0" lIns="91440" tIns="45720" rIns="91440" bIns="45720" vert="horz" wrap="square" numCol="1" rtlCol="0" anchor="t" anchorCtr="0">
-          <a:prstTxWarp prst="textNoShape"/>
+        <a:bodyPr vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:p>
@@ -674,27 +1434,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="E-1"/>
-      <sheetName val="E-2"/>
-      <sheetName val="E-3"/>
-      <sheetName val="E-4"/>
-      <sheetName val="E-5"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -740,7 +1479,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -773,26 +1512,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -825,23 +1547,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -983,439 +1688,468 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91d2775c-0681-4300-a5b9-2ec76c064f97}">
-  <dimension ref="A1:AF15"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:AF16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
   <sheetData>
-    <row r="1" spans="1:32" ht="15">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="15" spans="1:32">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
-      <c r="Z1" s="2"/>
-      <c r="AA1" s="2"/>
-      <c r="AB1" s="2"/>
-      <c r="AC1" s="2"/>
-      <c r="AD1" s="2"/>
-      <c r="AE1" s="2"/>
-      <c r="AF1" s="2"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
     </row>
-    <row r="2" spans="1:32" ht="15">
-      <c r="A2" s="2" t="s">
+    <row r="2" ht="15" spans="1:32">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
-      <c r="X2" s="2"/>
-      <c r="Y2" s="2"/>
-      <c r="Z2" s="2"/>
-      <c r="AA2" s="2"/>
-      <c r="AB2" s="2"/>
-      <c r="AC2" s="2"/>
-      <c r="AD2" s="2"/>
-      <c r="AE2" s="2"/>
-      <c r="AF2" s="2"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
     </row>
-    <row r="3" spans="1:32" ht="15">
-      <c r="A3" s="2" t="s">
+    <row r="3" ht="15" spans="1:32">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2"/>
-      <c r="T3" s="2"/>
-      <c r="U3" s="2"/>
-      <c r="V3" s="2"/>
-      <c r="W3" s="2"/>
-      <c r="X3" s="2"/>
-      <c r="Y3" s="2"/>
-      <c r="Z3" s="2"/>
-      <c r="AA3" s="2"/>
-      <c r="AB3" s="2"/>
-      <c r="AC3" s="2"/>
-      <c r="AD3" s="2"/>
-      <c r="AE3" s="2"/>
-      <c r="AF3" s="2"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="1"/>
+      <c r="W3" s="1"/>
+      <c r="X3" s="1"/>
+      <c r="Y3" s="1"/>
+      <c r="Z3" s="1"/>
+      <c r="AA3" s="1"/>
+      <c r="AB3" s="1"/>
+      <c r="AC3" s="1"/>
+      <c r="AD3" s="1"/>
+      <c r="AE3" s="1"/>
+      <c r="AF3" s="1"/>
     </row>
-    <row r="4" spans="1:32" ht="15">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2"/>
-      <c r="T4" s="2"/>
-      <c r="U4" s="2"/>
-      <c r="V4" s="2"/>
-      <c r="W4" s="2"/>
-      <c r="X4" s="2"/>
-      <c r="Y4" s="2"/>
-      <c r="Z4" s="2"/>
-      <c r="AA4" s="2"/>
-      <c r="AB4" s="2"/>
-      <c r="AC4" s="2"/>
-      <c r="AD4" s="2"/>
-      <c r="AE4" s="2"/>
-      <c r="AF4" s="2"/>
+    <row r="4" ht="15" spans="1:32">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
+      <c r="U4" s="1"/>
+      <c r="V4" s="1"/>
+      <c r="W4" s="1"/>
+      <c r="X4" s="1"/>
+      <c r="Y4" s="1"/>
+      <c r="Z4" s="1"/>
+      <c r="AA4" s="1"/>
+      <c r="AB4" s="1"/>
+      <c r="AC4" s="1"/>
+      <c r="AD4" s="1"/>
+      <c r="AE4" s="1"/>
+      <c r="AF4" s="1"/>
     </row>
-    <row r="5" spans="1:1" ht="15">
-      <c r="A5" s="1" t="s">
+    <row r="5" ht="15" spans="1:1">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="15">
-      <c r="A6" s="1" t="s">
+    <row r="6" ht="15" spans="1:1">
+      <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="15">
-      <c r="A7" s="1" t="s">
+    <row r="7" ht="15" spans="1:1">
+      <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="15">
-      <c r="A8" s="1" t="s">
+    <row r="8" ht="15" spans="1:1">
+      <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="15">
-      <c r="A9" s="1" t="s">
+    <row r="9" ht="15" spans="1:1">
+      <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="15">
-      <c r="A10" s="1" t="s">
+    <row r="10" ht="15" spans="1:1">
+      <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" ht="15.75" thickBot="1"/>
-    <row r="12" spans="1:32" ht="21.75" thickBot="1">
-      <c r="A12" s="3" t="s">
+    <row r="12" ht="21.75" spans="1:32">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+      <c r="S12" s="3"/>
+      <c r="T12" s="3"/>
+      <c r="U12" s="3"/>
+      <c r="V12" s="3"/>
+      <c r="W12" s="3"/>
+      <c r="X12" s="3"/>
+      <c r="Y12" s="3"/>
+      <c r="Z12" s="3"/>
+      <c r="AA12" s="3"/>
+      <c r="AB12" s="3"/>
+      <c r="AC12" s="3"/>
+      <c r="AD12" s="3"/>
+      <c r="AE12" s="3"/>
+      <c r="AF12" s="3"/>
+    </row>
+    <row r="13" ht="21.75" spans="1:32">
+      <c r="A13" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
-      <c r="Q12" s="4"/>
-      <c r="R12" s="4"/>
-      <c r="S12" s="4"/>
-      <c r="T12" s="4"/>
-      <c r="U12" s="4"/>
-      <c r="V12" s="4"/>
-      <c r="W12" s="4"/>
-      <c r="X12" s="4"/>
-      <c r="Y12" s="4"/>
-      <c r="Z12" s="4"/>
-      <c r="AA12" s="4"/>
-      <c r="AB12" s="4"/>
-      <c r="AC12" s="4"/>
-      <c r="AD12" s="4"/>
-      <c r="AE12" s="4"/>
-      <c r="AF12" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="5"/>
+      <c r="S13" s="5"/>
+      <c r="T13" s="5"/>
+      <c r="U13" s="5"/>
+      <c r="V13" s="5"/>
+      <c r="W13" s="5"/>
+      <c r="X13" s="5"/>
+      <c r="Y13" s="5"/>
+      <c r="Z13" s="5"/>
+      <c r="AA13" s="5"/>
+      <c r="AB13" s="5"/>
+      <c r="AC13" s="5"/>
+      <c r="AD13" s="5"/>
+      <c r="AE13" s="5"/>
+      <c r="AF13" s="29"/>
     </row>
-    <row r="13" spans="1:32" ht="15" customHeight="1">
-      <c r="A13" s="6" t="s">
+    <row r="14" ht="15" customHeight="1" spans="1:32">
+      <c r="A14" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B14" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C14" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D14" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E14" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F14" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="G14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H14" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="I13" s="10" t="s">
+      <c r="I14" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J13" s="10" t="s">
+      <c r="J14" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="K13" s="10" t="s">
+      <c r="K14" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="L13" s="11" t="s">
+      <c r="L14" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="12" t="s">
+      <c r="M14" s="21"/>
+      <c r="N14" s="21"/>
+      <c r="O14" s="21"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="21"/>
+      <c r="R14" s="21"/>
+      <c r="S14" s="21"/>
+      <c r="T14" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="U13" s="12"/>
-      <c r="V13" s="12"/>
-      <c r="W13" s="12"/>
-      <c r="X13" s="12"/>
-      <c r="Y13" s="12"/>
-      <c r="Z13" s="7" t="s">
+      <c r="U14" s="24"/>
+      <c r="V14" s="24"/>
+      <c r="W14" s="24"/>
+      <c r="X14" s="24"/>
+      <c r="Y14" s="24"/>
+      <c r="Z14" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="AA13" s="7" t="s">
+      <c r="AA14" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="AB13" s="7" t="s">
+      <c r="AB14" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="AC13" s="7" t="s">
+      <c r="AC14" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AD13" s="7" t="s">
+      <c r="AD14" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="AE13" s="7" t="s">
+      <c r="AE14" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="AF13" s="13" t="s">
+      <c r="AF14" s="30" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:32" ht="15">
-      <c r="A14" s="14"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="18"/>
-      <c r="K14" s="18"/>
-      <c r="L14" s="19" t="s">
+    <row r="15" ht="15" spans="1:32">
+      <c r="A15" s="11"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="M14" s="19"/>
-      <c r="N14" s="19"/>
-      <c r="O14" s="19"/>
-      <c r="P14" s="19"/>
-      <c r="Q14" s="20" t="s">
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22"/>
+      <c r="P15" s="22"/>
+      <c r="Q15" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="R14" s="20" t="s">
+      <c r="R15" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="S14" s="20" t="s">
+      <c r="S15" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="T14" s="21" t="s">
+      <c r="T15" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="U14" s="21"/>
-      <c r="V14" s="21"/>
-      <c r="W14" s="22" t="s">
+      <c r="U15" s="26"/>
+      <c r="V15" s="26"/>
+      <c r="W15" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="X14" s="22" t="s">
+      <c r="X15" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="Y14" s="22" t="s">
+      <c r="Y15" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="Z14" s="15"/>
-      <c r="AA14" s="15"/>
-      <c r="AB14" s="15"/>
-      <c r="AC14" s="15"/>
-      <c r="AD14" s="15"/>
-      <c r="AE14" s="15"/>
-      <c r="AF14" s="23"/>
+      <c r="Z15" s="12"/>
+      <c r="AA15" s="12"/>
+      <c r="AB15" s="12"/>
+      <c r="AC15" s="12"/>
+      <c r="AD15" s="12"/>
+      <c r="AE15" s="12"/>
+      <c r="AF15" s="31"/>
     </row>
-    <row r="15" spans="1:32" ht="30.75" thickBot="1">
-      <c r="A15" s="24"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="28"/>
-      <c r="J15" s="28"/>
-      <c r="K15" s="28"/>
-      <c r="L15" s="29" t="s">
+    <row r="16" ht="30.75" spans="1:32">
+      <c r="A16" s="16"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="M15" s="29" t="s">
+      <c r="M16" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="N15" s="29" t="s">
+      <c r="N16" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="O15" s="29" t="s">
+      <c r="O16" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="P15" s="29" t="s">
+      <c r="P16" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="Q15" s="29"/>
-      <c r="R15" s="29"/>
-      <c r="S15" s="29"/>
-      <c r="T15" s="30" t="s">
+      <c r="Q16" s="23"/>
+      <c r="R16" s="23"/>
+      <c r="S16" s="23"/>
+      <c r="T16" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="U15" s="30" t="s">
+      <c r="U16" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="V15" s="30" t="s">
+      <c r="V16" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="W15" s="30"/>
-      <c r="X15" s="30"/>
-      <c r="Y15" s="30"/>
-      <c r="Z15" s="25"/>
-      <c r="AA15" s="25"/>
-      <c r="AB15" s="25"/>
-      <c r="AC15" s="25"/>
-      <c r="AD15" s="25"/>
-      <c r="AE15" s="25"/>
-      <c r="AF15" s="31"/>
+      <c r="W16" s="28"/>
+      <c r="X16" s="28"/>
+      <c r="Y16" s="28"/>
+      <c r="Z16" s="17"/>
+      <c r="AA16" s="17"/>
+      <c r="AB16" s="17"/>
+      <c r="AC16" s="17"/>
+      <c r="AD16" s="17"/>
+      <c r="AE16" s="17"/>
+      <c r="AF16" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="32">
     <mergeCell ref="A1:AF1"/>
     <mergeCell ref="A2:AF2"/>
     <mergeCell ref="A3:AF3"/>
-    <mergeCell ref="A12:AF12"/>
-    <mergeCell ref="L14:P14"/>
-    <mergeCell ref="L13:S13"/>
-    <mergeCell ref="T13:Y13"/>
-    <mergeCell ref="T14:V14"/>
-    <mergeCell ref="K13:K15"/>
-    <mergeCell ref="J13:J15"/>
-    <mergeCell ref="Y14:Y15"/>
-    <mergeCell ref="X14:X15"/>
-    <mergeCell ref="W14:W15"/>
-    <mergeCell ref="I13:I15"/>
-    <mergeCell ref="H13:H15"/>
-    <mergeCell ref="B13:B15"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="S14:S15"/>
-    <mergeCell ref="R14:R15"/>
-    <mergeCell ref="Q14:Q15"/>
-    <mergeCell ref="G13:G15"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="F13:F15"/>
-    <mergeCell ref="Z13:Z15"/>
-    <mergeCell ref="AF13:AF15"/>
-    <mergeCell ref="AE13:AE15"/>
-    <mergeCell ref="AD13:AD15"/>
-    <mergeCell ref="AC13:AC15"/>
-    <mergeCell ref="AB13:AB15"/>
-    <mergeCell ref="AA13:AA15"/>
+    <mergeCell ref="A13:AF13"/>
+    <mergeCell ref="L14:S14"/>
+    <mergeCell ref="T14:Y14"/>
+    <mergeCell ref="L15:P15"/>
+    <mergeCell ref="T15:V15"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="H14:H16"/>
+    <mergeCell ref="I14:I16"/>
+    <mergeCell ref="J14:J16"/>
+    <mergeCell ref="K14:K16"/>
+    <mergeCell ref="Q15:Q16"/>
+    <mergeCell ref="R15:R16"/>
+    <mergeCell ref="S15:S16"/>
+    <mergeCell ref="W15:W16"/>
+    <mergeCell ref="X15:X16"/>
+    <mergeCell ref="Y15:Y16"/>
+    <mergeCell ref="Z14:Z16"/>
+    <mergeCell ref="AA14:AA16"/>
+    <mergeCell ref="AB14:AB16"/>
+    <mergeCell ref="AC14:AC16"/>
+    <mergeCell ref="AD14:AD16"/>
+    <mergeCell ref="AE14:AE16"/>
+    <mergeCell ref="AF14:AF16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>